--- a/Axam_Results.xlsx
+++ b/Axam_Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2025/Ghana_Project/QA1_&amp;_3/Documentation/axam-docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5479B3C-A227-5B45-8A7A-C8D22E1E9B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9EDBFA2-B3FF-964C-850A-8F458DD82AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{AA4B684E-F9E2-7F41-996C-BD2AB92E0EF7}"/>
+    <workbookView xWindow="6260" yWindow="1440" windowWidth="29400" windowHeight="18480" activeTab="2" xr2:uid="{AA4B684E-F9E2-7F41-996C-BD2AB92E0EF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Net ERs" sheetId="1" r:id="rId1"/>
@@ -18428,7 +18428,7 @@
         <v>224</v>
       </c>
       <c r="B7">
-        <f t="shared" si="0"/>
+        <f>C7/$C$9 * 45000*0.2</f>
         <v>124.13793103448278</v>
       </c>
       <c r="C7">

--- a/Axam_Results.xlsx
+++ b/Axam_Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2025/Ghana_Project/QA1_&amp;_3/Documentation/axam-docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9EDBFA2-B3FF-964C-850A-8F458DD82AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EAF447-C71E-2E42-8BD5-0304DF78A565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6260" yWindow="1440" windowWidth="29400" windowHeight="18480" activeTab="2" xr2:uid="{AA4B684E-F9E2-7F41-996C-BD2AB92E0EF7}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{AA4B684E-F9E2-7F41-996C-BD2AB92E0EF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Net ERs" sheetId="1" r:id="rId1"/>
@@ -2108,10 +2108,10 @@
       <c r="A5" t="s">
         <v>235</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -2150,18 +2150,18 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>11.5275375636592</v>
+        <v>36.164812949999998</v>
       </c>
       <c r="C6">
-        <v>3.5605292727663098</v>
+        <v>28.225958439999999</v>
       </c>
       <c r="D6">
         <f t="shared" ref="D6:D18" si="0">(B6 -C6)</f>
-        <v>7.9670082908928901</v>
+        <v>7.9388545099999988</v>
       </c>
       <c r="F6" s="3">
-        <f t="shared" ref="F6:F18" si="1">D6*$B$2*44/12</f>
-        <v>262911.27359946538</v>
+        <f>D6*$B$2*44/12</f>
+        <v>261982.19882999992</v>
       </c>
       <c r="Q6" s="126" t="s">
         <v>256</v>
@@ -2193,18 +2193,18 @@
         <v>2025</v>
       </c>
       <c r="B7">
-        <v>11.5275365866203</v>
+        <v>36.164813930000001</v>
       </c>
       <c r="C7">
-        <v>3.5605283073246401</v>
+        <v>28.225957480000002</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>7.9670082792956602</v>
+        <v>7.9388564499999994</v>
       </c>
       <c r="F7" s="3">
-        <f t="shared" si="1"/>
-        <v>262911.27321675682</v>
+        <f t="shared" ref="F7:F18" si="1">D7*$B$2*44/12</f>
+        <v>261982.26285000003</v>
       </c>
       <c r="G7">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="U7" s="123">
         <f>(W7+V7)*0.175</f>
-        <v>43639.013978318224</v>
+        <v>43476.437164135787</v>
       </c>
       <c r="V7">
         <f>R7-S7</f>
@@ -2256,11 +2256,11 @@
       </c>
       <c r="W7" s="123">
         <f>F7-G7</f>
-        <v>245580.66047159847</v>
+        <v>244651.65010484168</v>
       </c>
       <c r="X7" s="123">
         <f>W7+V7-U7</f>
-        <v>205726.78018350023</v>
+        <v>204960.34663092589</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
@@ -2268,18 +2268,18 @@
         <v>2026</v>
       </c>
       <c r="B8">
-        <v>11.527535628049</v>
+        <v>36.164814890000002</v>
       </c>
       <c r="C8">
-        <v>3.56052736013143</v>
+        <v>28.619948829999998</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>7.9670082679175698</v>
+        <v>7.5448660600000039</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>262911.2728412798</v>
+        <v>248980.57998000013</v>
       </c>
       <c r="G8">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="U8" s="123">
         <f t="shared" ref="U8:U47" si="5">(W8+V8)*0.175</f>
-        <v>43639.013912609749</v>
+        <v>41201.14266188581</v>
       </c>
       <c r="V8">
         <f t="shared" ref="V8:V47" si="6">R8-S8</f>
@@ -2331,11 +2331,11 @@
       </c>
       <c r="W8" s="123">
         <f t="shared" ref="W8:W47" si="7">F8-G8</f>
-        <v>245580.66009612146</v>
+        <v>231649.96723484178</v>
       </c>
       <c r="X8" s="123">
         <f t="shared" ref="X8:X47" si="8">W8+V8-U8</f>
-        <v>205726.77987373169</v>
+        <v>194233.95826317597</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.2">
@@ -2343,18 +2343,18 @@
         <v>2027</v>
       </c>
       <c r="B9">
-        <v>11.527534687596299</v>
+        <v>36.164815840000003</v>
       </c>
       <c r="C9">
-        <v>3.5605264308417599</v>
+        <v>28.246774009999999</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>7.9670082567545393</v>
+        <v>7.9180418300000035</v>
       </c>
       <c r="F9" s="3">
         <f t="shared" si="1"/>
-        <v>262911.27247289981</v>
+        <v>261295.38039000009</v>
       </c>
       <c r="G9">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="U9" s="123">
         <f t="shared" si="5"/>
-        <v>43639.013848143251</v>
+        <v>43356.232733635799</v>
       </c>
       <c r="V9">
         <f t="shared" si="6"/>
@@ -2406,11 +2406,11 @@
       </c>
       <c r="W9" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65972774147</v>
+        <v>243964.76764484175</v>
       </c>
       <c r="X9" s="123">
         <f t="shared" si="8"/>
-        <v>205726.7795698182</v>
+        <v>204393.66860142595</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
@@ -2418,18 +2418,18 @@
         <v>2028</v>
       </c>
       <c r="B10">
-        <v>11.5275337649198</v>
+        <v>36.164816760000001</v>
       </c>
       <c r="C10">
-        <v>3.56052551911722</v>
+        <v>28.240847299999999</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>7.9670082458025799</v>
+        <v>7.9239694600000021</v>
       </c>
       <c r="F10" s="3">
         <f t="shared" si="1"/>
-        <v>262911.27211148513</v>
+        <v>261490.99218000009</v>
       </c>
       <c r="G10">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="U10" s="123">
         <f t="shared" si="5"/>
-        <v>43639.01378489568</v>
+        <v>43390.464796885797</v>
       </c>
       <c r="V10">
         <f t="shared" si="6"/>
@@ -2481,11 +2481,11 @@
       </c>
       <c r="W10" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65936632678</v>
+        <v>244160.37943484174</v>
       </c>
       <c r="X10" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77927165109</v>
+        <v>204555.04832817594</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
@@ -2493,18 +2493,18 @@
         <v>2029</v>
       </c>
       <c r="B11">
-        <v>11.527532859683401</v>
+        <v>36.164817669999998</v>
       </c>
       <c r="C11">
-        <v>3.5605246246257898</v>
+        <v>28.2366928</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>7.9670082350576106</v>
+        <v>7.9281248699999978</v>
       </c>
       <c r="F11" s="3">
         <f t="shared" si="1"/>
-        <v>262911.27175690111</v>
+        <v>261628.12070999993</v>
       </c>
       <c r="G11">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="U11" s="123">
         <f t="shared" si="5"/>
-        <v>43639.013722843476</v>
+        <v>43414.462289635769</v>
       </c>
       <c r="V11">
         <f t="shared" si="6"/>
@@ -2556,11 +2556,11 @@
       </c>
       <c r="W11" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65901174277</v>
+        <v>244297.50796484158</v>
       </c>
       <c r="X11" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77897911926</v>
+        <v>204668.17936542581</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.2">
@@ -2568,18 +2568,18 @@
         <v>2030</v>
       </c>
       <c r="B12">
-        <v>11.5275319715574</v>
+        <v>36.164818560000001</v>
       </c>
       <c r="C12">
-        <v>3.5605237470417501</v>
+        <v>28.233756159999999</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>7.9670082245156495</v>
+        <v>7.9310624000000018</v>
       </c>
       <c r="F12" s="3">
         <f t="shared" si="1"/>
-        <v>262911.27140901645</v>
+        <v>261725.05920000005</v>
       </c>
       <c r="G12">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="U12" s="123">
         <f t="shared" si="5"/>
-        <v>43639.013661963661</v>
+        <v>43431.426525385796</v>
       </c>
       <c r="V12">
         <f t="shared" si="6"/>
@@ -2631,11 +2631,11 @@
       </c>
       <c r="W12" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65866385811</v>
+        <v>244394.4464548417</v>
       </c>
       <c r="X12" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77869211443</v>
+        <v>204748.1536196759</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.2">
@@ -2643,18 +2643,18 @@
         <v>2031</v>
       </c>
       <c r="B13">
-        <v>11.527531100218599</v>
+        <v>36.164819440000002</v>
       </c>
       <c r="C13">
-        <v>3.5605228860455198</v>
+        <v>28.23166866</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>7.9670082141730791</v>
+        <v>7.9331507800000018</v>
       </c>
       <c r="F13" s="3">
         <f t="shared" si="1"/>
-        <v>262911.27106771158</v>
+        <v>261793.97574000002</v>
       </c>
       <c r="G13">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="U13" s="123">
         <f t="shared" si="5"/>
-        <v>43639.013602235311</v>
+        <v>43443.486919885785</v>
       </c>
       <c r="V13">
         <f t="shared" si="6"/>
@@ -2706,11 +2706,11 @@
       </c>
       <c r="W13" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65832255324</v>
+        <v>244463.36299484168</v>
       </c>
       <c r="X13" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77841053793</v>
+        <v>204805.00976517587</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.2">
@@ -2718,18 +2718,18 @@
         <v>2032</v>
       </c>
       <c r="B14">
-        <v>11.527530245349499</v>
+        <v>36.164820300000002</v>
       </c>
       <c r="C14">
-        <v>3.5605220413235599</v>
+        <v>28.230178179999999</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>7.9670082040259391</v>
+        <v>7.934642120000003</v>
       </c>
       <c r="F14" s="3">
         <f t="shared" si="1"/>
-        <v>262911.27073285601</v>
+        <v>261843.18996000008</v>
       </c>
       <c r="G14">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="U14" s="123">
         <f t="shared" si="5"/>
-        <v>43639.013543635585</v>
+        <v>43452.099408385795</v>
       </c>
       <c r="V14">
         <f t="shared" si="6"/>
@@ -2781,11 +2781,11 @@
       </c>
       <c r="W14" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65798769766</v>
+        <v>244512.57721484173</v>
       </c>
       <c r="X14" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77813428207</v>
+        <v>204845.61149667593</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.2">
@@ -2793,18 +2793,18 @@
         <v>2033</v>
       </c>
       <c r="B15">
-        <v>11.5275294066389</v>
+        <v>36.164821140000001</v>
       </c>
       <c r="C15">
-        <v>3.5605212125682599</v>
+        <v>28.22911015</v>
       </c>
       <c r="D15">
         <f t="shared" si="0"/>
-        <v>7.9670081940706403</v>
+        <v>7.9357109900000005</v>
       </c>
       <c r="F15" s="3">
         <f t="shared" si="1"/>
-        <v>262911.27040433115</v>
+        <v>261878.46267000001</v>
       </c>
       <c r="G15">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="U15" s="123">
         <f t="shared" si="5"/>
-        <v>43639.013486143733</v>
+        <v>43458.272132635786</v>
       </c>
       <c r="V15">
         <f t="shared" si="6"/>
@@ -2856,11 +2856,11 @@
       </c>
       <c r="W15" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65765917281</v>
+        <v>244547.84992484166</v>
       </c>
       <c r="X15" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77786324907</v>
+        <v>204874.71148242586</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.2">
@@ -2868,18 +2868,18 @@
         <v>2034</v>
       </c>
       <c r="B16">
-        <v>11.5275285837812</v>
+        <v>36.164821959999998</v>
       </c>
       <c r="C16">
-        <v>3.5605203994778098</v>
+        <v>28.228342510000001</v>
       </c>
       <c r="D16">
         <f t="shared" si="0"/>
-        <v>7.9670081843033902</v>
+        <v>7.9364794499999967</v>
       </c>
       <c r="F16" s="3">
         <f t="shared" si="1"/>
-        <v>262911.27008201188</v>
+        <v>261903.82184999992</v>
       </c>
       <c r="G16">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="U16" s="123">
         <f t="shared" si="5"/>
-        <v>43639.013429737861</v>
+        <v>43462.709989135772</v>
       </c>
       <c r="V16">
         <f t="shared" si="6"/>
@@ -2931,11 +2931,11 @@
       </c>
       <c r="W16" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65733685353</v>
+        <v>244573.20910484158</v>
       </c>
       <c r="X16" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77759733566</v>
+        <v>204895.63280592579</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.2">
@@ -2943,18 +2943,18 @@
         <v>2035</v>
       </c>
       <c r="B17">
-        <v>11.527527776476999</v>
+        <v>36.164822770000001</v>
       </c>
       <c r="C17">
-        <v>3.5605196017561398</v>
+        <v>28.227789219999998</v>
       </c>
       <c r="D17">
         <f t="shared" si="0"/>
-        <v>7.9670081747208599</v>
+        <v>7.9370335500000024</v>
       </c>
       <c r="F17" s="3">
         <f t="shared" si="1"/>
-        <v>262911.2697657884</v>
+        <v>261922.10715000008</v>
       </c>
       <c r="G17">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="U17" s="123">
         <f>(W17+V17)*0.175</f>
-        <v>43639.013374398754</v>
+        <v>43465.909916635799</v>
       </c>
       <c r="V17">
         <f t="shared" si="6"/>
@@ -3006,11 +3006,11 @@
       </c>
       <c r="W17" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65702063005</v>
+        <v>244591.49440484174</v>
       </c>
       <c r="X17" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77733645128</v>
+        <v>204910.71817842592</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.2">
@@ -3018,18 +3018,18 @@
         <v>2036</v>
       </c>
       <c r="B18">
-        <v>11.5275269844322</v>
+        <v>36.164823570000003</v>
       </c>
       <c r="C18">
-        <v>3.5605188191127399</v>
+        <v>28.227389330000001</v>
       </c>
       <c r="D18">
         <f t="shared" si="0"/>
-        <v>7.9670081653194593</v>
+        <v>7.9374342400000018</v>
       </c>
       <c r="F18" s="3">
         <f t="shared" si="1"/>
-        <v>262911.26945554215</v>
+        <v>261935.32992000008</v>
       </c>
       <c r="G18">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="U18" s="123">
         <f t="shared" si="5"/>
-        <v>43639.01332010566</v>
+        <v>43468.223901385798</v>
       </c>
       <c r="V18">
         <f t="shared" si="6"/>
@@ -3081,11 +3081,11 @@
       </c>
       <c r="W18" s="123">
         <f t="shared" si="7"/>
-        <v>245580.6567103838</v>
+        <v>244604.71717484173</v>
       </c>
       <c r="X18" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77708049811</v>
+        <v>204921.62696367592</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
@@ -3093,18 +3093,18 @@
         <v>2037</v>
       </c>
       <c r="B19">
-        <v>11.527526207358401</v>
+        <v>36.164824350000004</v>
       </c>
       <c r="C19">
-        <v>3.5605180512626098</v>
+        <v>28.227099419999998</v>
       </c>
       <c r="D19">
         <f t="shared" ref="D19:D47" si="9">(B19 -C19)</f>
-        <v>7.9670081560957904</v>
+        <v>7.9377249300000052</v>
       </c>
       <c r="F19" s="3">
         <f t="shared" ref="F19:F47" si="10">D19*$B$2*44/12</f>
-        <v>262911.26915116108</v>
+        <v>261944.92269000015</v>
       </c>
       <c r="G19">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="U19" s="123">
         <f t="shared" si="5"/>
-        <v>43639.013266838971</v>
+        <v>43469.902636135812</v>
       </c>
       <c r="V19">
         <f t="shared" si="6"/>
@@ -3156,11 +3156,11 @@
       </c>
       <c r="W19" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65640600273</v>
+        <v>244614.30994484181</v>
       </c>
       <c r="X19" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77682938374</v>
+        <v>204929.54099892598</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.2">
@@ -3168,18 +3168,18 @@
         <v>2038</v>
       </c>
       <c r="B20">
-        <v>11.5275254449725</v>
+        <v>36.164825110000002</v>
       </c>
       <c r="C20">
-        <v>3.5605172979261401</v>
+        <v>28.226888509999998</v>
       </c>
       <c r="D20">
         <f t="shared" si="9"/>
-        <v>7.9670081470463607</v>
+        <v>7.937936600000004</v>
       </c>
       <c r="F20" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26885252993</v>
+        <v>261951.90780000013</v>
       </c>
       <c r="G20">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="U20" s="123">
         <f t="shared" si="5"/>
-        <v>43639.013214578525</v>
+        <v>43471.125030385811</v>
       </c>
       <c r="V20">
         <f t="shared" si="6"/>
@@ -3231,11 +3231,11 @@
       </c>
       <c r="W20" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65610737159</v>
+        <v>244621.29505484179</v>
       </c>
       <c r="X20" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77658301304</v>
+        <v>204935.30371467595</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.2">
@@ -3243,18 +3243,18 @@
         <v>2039</v>
       </c>
       <c r="B21">
-        <v>11.527524696997</v>
+        <v>36.164825860000001</v>
       </c>
       <c r="C21">
-        <v>3.5605165588289802</v>
+        <v>28.226734400000002</v>
       </c>
       <c r="D21">
         <f t="shared" si="9"/>
-        <v>7.96700813816802</v>
+        <v>7.938091459999999</v>
       </c>
       <c r="F21" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26855954464</v>
+        <v>261957.01817999998</v>
       </c>
       <c r="G21">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="U21" s="123">
         <f t="shared" si="5"/>
-        <v>43639.013163306096</v>
+        <v>43472.019346885783</v>
       </c>
       <c r="V21">
         <f t="shared" si="6"/>
@@ -3306,11 +3306,11 @@
       </c>
       <c r="W21" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65581438629</v>
+        <v>244626.40543484164</v>
       </c>
       <c r="X21" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77634130017</v>
+        <v>204939.51977817583</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.2">
@@ -3318,18 +3318,18 @@
         <v>2040</v>
       </c>
       <c r="B22">
-        <v>11.527523963159499</v>
+        <v>36.164826599999998</v>
       </c>
       <c r="C22">
-        <v>3.560515833702</v>
+        <v>28.226621170000001</v>
       </c>
       <c r="D22">
         <f t="shared" si="9"/>
-        <v>7.9670081294574988</v>
+        <v>7.9382054299999965</v>
       </c>
       <c r="F22" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26827209746</v>
+        <v>261960.77918999991</v>
       </c>
       <c r="G22">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="U22" s="123">
         <f t="shared" si="5"/>
-        <v>43639.013113002839</v>
+        <v>43472.677523635772</v>
       </c>
       <c r="V22">
         <f t="shared" si="6"/>
@@ -3381,11 +3381,11 @@
       </c>
       <c r="W22" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65552693911</v>
+        <v>244630.16644484157</v>
       </c>
       <c r="X22" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77610415625</v>
+        <v>204942.62261142579</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.2">
@@ -3393,18 +3393,18 @@
         <v>2041</v>
       </c>
       <c r="B23">
-        <v>11.5275232431928</v>
+        <v>36.164827320000001</v>
       </c>
       <c r="C23">
-        <v>3.56051512228112</v>
+        <v>28.226537409999999</v>
       </c>
       <c r="D23">
         <f t="shared" si="9"/>
-        <v>7.9670081209116796</v>
+        <v>7.9382899100000017</v>
       </c>
       <c r="F23" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26799008541</v>
+        <v>261963.56703000006</v>
       </c>
       <c r="G23">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="U23" s="123">
         <f t="shared" si="5"/>
-        <v>43639.013063650731</v>
+        <v>43473.165395635799</v>
       </c>
       <c r="V23">
         <f t="shared" si="6"/>
@@ -3456,11 +3456,11 @@
       </c>
       <c r="W23" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65524492707</v>
+        <v>244632.95428484172</v>
       </c>
       <c r="X23" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77587149633</v>
+        <v>204944.92257942591</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.2">
@@ -3468,18 +3468,18 @@
         <v>2042</v>
       </c>
       <c r="B24">
-        <v>11.527522536834599</v>
+        <v>36.164828030000002</v>
       </c>
       <c r="C24">
-        <v>3.5605144243072999</v>
+        <v>28.226474889999999</v>
       </c>
       <c r="D24">
         <f t="shared" si="9"/>
-        <v>7.9670081125272993</v>
+        <v>7.9383531400000038</v>
       </c>
       <c r="F24" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26771340088</v>
+        <v>261965.65362000011</v>
       </c>
       <c r="G24">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="U24" s="123">
         <f t="shared" si="5"/>
-        <v>43639.013015230936</v>
+        <v>43473.530548885807</v>
       </c>
       <c r="V24">
         <f t="shared" si="6"/>
@@ -3531,11 +3531,11 @@
       </c>
       <c r="W24" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65496824254</v>
+        <v>244635.04087484177</v>
       </c>
       <c r="X24" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77564323158</v>
+        <v>204946.64401617594</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
@@ -3543,18 +3543,18 @@
         <v>2043</v>
       </c>
       <c r="B25">
-        <v>11.527521843827801</v>
+        <v>36.164828730000004</v>
       </c>
       <c r="C25">
-        <v>3.56051373952634</v>
+        <v>28.226427709999999</v>
       </c>
       <c r="D25">
         <f t="shared" si="9"/>
-        <v>7.9670081043014607</v>
+        <v>7.9384010200000041</v>
       </c>
       <c r="F25" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26744194818</v>
+        <v>261967.23366000014</v>
       </c>
       <c r="G25">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="U25" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012967726718</v>
+        <v>43473.807055885809</v>
       </c>
       <c r="V25">
         <f t="shared" si="6"/>
@@ -3606,11 +3606,11 @@
       </c>
       <c r="W25" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65469678983</v>
+        <v>244636.6209148418</v>
       </c>
       <c r="X25" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77541928311</v>
+        <v>204947.94754917597</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.2">
@@ -3618,18 +3618,18 @@
         <v>2044</v>
       </c>
       <c r="B26">
-        <v>11.527521163919999</v>
+        <v>36.164829410000003</v>
       </c>
       <c r="C26">
-        <v>3.5605130676889001</v>
+        <v>28.226391620000001</v>
       </c>
       <c r="D26">
         <f t="shared" si="9"/>
-        <v>7.9670080962310994</v>
+        <v>7.9384377900000018</v>
       </c>
       <c r="F26" s="3">
         <f t="shared" si="10"/>
-        <v>262911.2671756263</v>
+        <v>261968.44707000002</v>
       </c>
       <c r="G26">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="U26" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012921120389</v>
+        <v>43474.019402635786</v>
       </c>
       <c r="V26">
         <f t="shared" si="6"/>
@@ -3681,11 +3681,11 @@
       </c>
       <c r="W26" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65443046796</v>
+        <v>244637.83432484168</v>
       </c>
       <c r="X26" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77519956755</v>
+        <v>204948.94861242588</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
@@ -3693,18 +3693,18 @@
         <v>2045</v>
       </c>
       <c r="B27">
-        <v>11.5275204968636</v>
+        <v>36.164830080000002</v>
       </c>
       <c r="C27">
-        <v>3.5605124085502999</v>
+        <v>28.226363549999999</v>
       </c>
       <c r="D27">
         <f t="shared" si="9"/>
-        <v>7.9670080883132997</v>
+        <v>7.938466530000003</v>
       </c>
       <c r="F27" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26691433892</v>
+        <v>261969.39549000011</v>
       </c>
       <c r="G27">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="U27" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012875395092</v>
+        <v>43474.185376135807</v>
       </c>
       <c r="V27">
         <f t="shared" si="6"/>
@@ -3756,11 +3756,11 @@
       </c>
       <c r="W27" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65416918058</v>
+        <v>244638.78274484177</v>
       </c>
       <c r="X27" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77498400546</v>
+        <v>204949.73105892594</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
@@ -3768,18 +3768,18 @@
         <v>2046</v>
       </c>
       <c r="B28">
-        <v>11.5275198424156</v>
+        <v>36.164830739999999</v>
       </c>
       <c r="C28">
-        <v>3.5605117618705302</v>
+        <v>28.226341300000001</v>
       </c>
       <c r="D28">
         <f t="shared" si="9"/>
-        <v>7.96700808054507</v>
+        <v>7.9384894399999979</v>
       </c>
       <c r="F28" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26665798732</v>
+        <v>261970.15151999996</v>
       </c>
       <c r="G28">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="U28" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012830533567</v>
+        <v>43474.317681385779</v>
       </c>
       <c r="V28">
         <f t="shared" si="6"/>
@@ -3831,11 +3831,11 @@
       </c>
       <c r="W28" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65391282897</v>
+        <v>244639.53877484161</v>
       </c>
       <c r="X28" s="123">
         <f t="shared" si="8"/>
-        <v>205726.7747725154</v>
+        <v>204950.35478367581</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.2">
@@ -3843,18 +3843,18 @@
         <v>2047</v>
       </c>
       <c r="B29">
-        <v>11.5275192003378</v>
+        <v>36.164831380000003</v>
       </c>
       <c r="C29">
-        <v>3.5605111274140802</v>
+        <v>28.226323279999999</v>
       </c>
       <c r="D29">
         <f t="shared" si="9"/>
-        <v>7.9670080729237194</v>
+        <v>7.9385081000000035</v>
       </c>
       <c r="F29" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26640648278</v>
+        <v>261970.76730000009</v>
       </c>
       <c r="G29">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="U29" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012786520274</v>
+        <v>43474.425442885804</v>
       </c>
       <c r="V29">
         <f t="shared" si="6"/>
@@ -3906,11 +3906,11 @@
       </c>
       <c r="W29" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65366132444</v>
+        <v>244640.15455484175</v>
       </c>
       <c r="X29" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77456502416</v>
+        <v>204950.86280217592</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.2">
@@ -3918,18 +3918,18 @@
         <v>2048</v>
       </c>
       <c r="B30">
-        <v>11.527518570396399</v>
+        <v>36.164832009999998</v>
       </c>
       <c r="C30">
-        <v>3.5605105049499302</v>
+        <v>28.22630835</v>
       </c>
       <c r="D30">
         <f t="shared" si="9"/>
-        <v>7.9670080654464694</v>
+        <v>7.9385236599999978</v>
       </c>
       <c r="F30" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26615973347</v>
+        <v>261971.28077999994</v>
       </c>
       <c r="G30">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="U30" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012743339139</v>
+        <v>43474.515301885775</v>
       </c>
       <c r="V30">
         <f t="shared" si="6"/>
@@ -3981,11 +3981,11 @@
       </c>
       <c r="W30" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65341457512</v>
+        <v>244640.6680348416</v>
       </c>
       <c r="X30" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77436145596</v>
+        <v>204951.2864231758</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.2">
@@ -3993,18 +3993,18 @@
         <v>2049</v>
       </c>
       <c r="B31">
-        <v>11.527517952361899</v>
+        <v>36.164832629999999</v>
       </c>
       <c r="C31">
-        <v>3.56050989425139</v>
+        <v>28.22629568</v>
       </c>
       <c r="D31">
         <f t="shared" si="9"/>
-        <v>7.9670080581105092</v>
+        <v>7.9385369499999996</v>
       </c>
       <c r="F31" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26591764682</v>
+        <v>261971.71935</v>
       </c>
       <c r="G31">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="U31" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012700973974</v>
+        <v>43474.592051635787</v>
       </c>
       <c r="V31">
         <f t="shared" si="6"/>
@@ -4056,11 +4056,11 @@
       </c>
       <c r="W31" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65317248847</v>
+        <v>244641.10660484165</v>
       </c>
       <c r="X31" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77416173447</v>
+        <v>204951.64824342585</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.2">
@@ -4068,18 +4068,18 @@
         <v>2050</v>
       </c>
       <c r="B32">
-        <v>11.527517346009301</v>
+        <v>36.16483324</v>
       </c>
       <c r="C32">
-        <v>3.5605092950960699</v>
+        <v>28.226284669999998</v>
       </c>
       <c r="D32">
         <f t="shared" si="9"/>
-        <v>7.9670080509132308</v>
+        <v>7.9385485700000018</v>
       </c>
       <c r="F32" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26568013662</v>
+        <v>261972.10281000007</v>
       </c>
       <c r="G32">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="U32" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012659409695</v>
+        <v>43474.659157135793</v>
       </c>
       <c r="V32">
         <f t="shared" si="6"/>
@@ -4131,11 +4131,11 @@
       </c>
       <c r="W32" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65293497828</v>
+        <v>244641.49006484172</v>
       </c>
       <c r="X32" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77396578857</v>
+        <v>204951.96459792592</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.2">
@@ -4143,18 +4143,18 @@
         <v>2051</v>
       </c>
       <c r="B33">
-        <v>11.527516751117799</v>
+        <v>36.16483384</v>
       </c>
       <c r="C33">
-        <v>3.5605087072657899</v>
+        <v>28.226274889999999</v>
       </c>
       <c r="D33">
         <f t="shared" si="9"/>
-        <v>7.9670080438520099</v>
+        <v>7.9385589500000009</v>
       </c>
       <c r="F33" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26544711634</v>
+        <v>261972.44535000005</v>
       </c>
       <c r="G33">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="U33" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012618631146</v>
+        <v>43474.71910163579</v>
       </c>
       <c r="V33">
         <f t="shared" si="6"/>
@@ -4206,11 +4206,11 @@
       </c>
       <c r="W33" s="123">
         <f t="shared" si="7"/>
-        <v>245580.652701958</v>
+        <v>244641.83260484171</v>
       </c>
       <c r="X33" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77377354683</v>
+        <v>204952.24719342589</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.2">
@@ -4218,18 +4218,18 @@
         <v>2052</v>
       </c>
       <c r="B34">
-        <v>11.527516167470701</v>
+        <v>36.164834419999998</v>
       </c>
       <c r="C34">
-        <v>3.5605081305464901</v>
+        <v>28.226266039999999</v>
       </c>
       <c r="D34">
         <f t="shared" si="9"/>
-        <v>7.9670080369242111</v>
+        <v>7.9385683799999995</v>
       </c>
       <c r="F34" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26521849894</v>
+        <v>261972.75654</v>
       </c>
       <c r="G34">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="U34" s="123">
         <f t="shared" si="5"/>
-        <v>43639.0125786231</v>
+        <v>43474.773559885783</v>
       </c>
       <c r="V34">
         <f t="shared" si="6"/>
@@ -4281,11 +4281,11 @@
       </c>
       <c r="W34" s="123">
         <f t="shared" si="7"/>
-        <v>245580.6524733406</v>
+        <v>244642.14379484166</v>
       </c>
       <c r="X34" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77358493747</v>
+        <v>204952.50392517587</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.2">
@@ -4293,18 +4293,18 @@
         <v>2053</v>
       </c>
       <c r="B35">
-        <v>11.527515594855499</v>
+        <v>36.164834999999997</v>
       </c>
       <c r="C35">
-        <v>3.5605075647281401</v>
+        <v>28.226257889999999</v>
       </c>
       <c r="D35">
         <f t="shared" si="9"/>
-        <v>7.9670080301273591</v>
+        <v>7.9385771099999971</v>
       </c>
       <c r="F35" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26499420282</v>
+        <v>261973.0446299999</v>
       </c>
       <c r="G35">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="U35" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012539371281</v>
+        <v>43474.823975635765</v>
       </c>
       <c r="V35">
         <f t="shared" si="6"/>
@@ -4356,11 +4356,11 @@
       </c>
       <c r="W35" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65224904448</v>
+        <v>244642.43188484156</v>
       </c>
       <c r="X35" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77339989319</v>
+        <v>204952.74159942579</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.2">
@@ -4368,18 +4368,18 @@
         <v>2054</v>
       </c>
       <c r="B36">
-        <v>11.5275150330637</v>
+        <v>36.16483556</v>
       </c>
       <c r="C36">
-        <v>3.5605070096047098</v>
+        <v>28.226250279999999</v>
       </c>
       <c r="D36">
         <f t="shared" si="9"/>
-        <v>7.9670080234589911</v>
+        <v>7.9385852800000016</v>
       </c>
       <c r="F36" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26477414666</v>
+        <v>261973.31424000001</v>
       </c>
       <c r="G36">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="U36" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012500861449</v>
+        <v>43474.871157385787</v>
       </c>
       <c r="V36">
         <f t="shared" si="6"/>
@@ -4431,11 +4431,11 @@
       </c>
       <c r="W36" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65202898832</v>
+        <v>244642.70149484166</v>
       </c>
       <c r="X36" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77321834685</v>
+        <v>204952.96402767586</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.2">
@@ -4443,18 +4443,18 @@
         <v>2055</v>
       </c>
       <c r="B37">
-        <v>11.5275144818907</v>
+        <v>36.164836119999997</v>
       </c>
       <c r="C37">
-        <v>3.5605064649740399</v>
+        <v>28.22624308</v>
       </c>
       <c r="D37">
         <f t="shared" si="9"/>
-        <v>7.9670080169166599</v>
+        <v>7.9385930399999971</v>
       </c>
       <c r="F37" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26455824979</v>
+        <v>261973.57031999991</v>
       </c>
       <c r="G37">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="U37" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012463079496</v>
+        <v>43474.915971385766</v>
       </c>
       <c r="V37">
         <f t="shared" si="6"/>
@@ -4506,11 +4506,11 @@
       </c>
       <c r="W37" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65181309145</v>
+        <v>244642.95757484157</v>
       </c>
       <c r="X37" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77304023193</v>
+        <v>204953.1752936758</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.2">
@@ -4518,18 +4518,18 @@
         <v>2056</v>
       </c>
       <c r="B38">
-        <v>11.527513941135799</v>
+        <v>36.164836659999999</v>
       </c>
       <c r="C38">
-        <v>3.5605059306378002</v>
+        <v>28.226236230000001</v>
       </c>
       <c r="D38">
         <f t="shared" si="9"/>
-        <v>7.9670080104979988</v>
+        <v>7.9386004299999975</v>
       </c>
       <c r="F38" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26434643398</v>
+        <v>261973.81418999992</v>
       </c>
       <c r="G38">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="U38" s="123">
         <f t="shared" si="5"/>
-        <v>43639.01242601173</v>
+        <v>43474.958648635773</v>
       </c>
       <c r="V38">
         <f t="shared" si="6"/>
@@ -4581,11 +4581,11 @@
       </c>
       <c r="W38" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65160127563</v>
+        <v>244643.20144484157</v>
       </c>
       <c r="X38" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77286548389</v>
+        <v>204953.37648642578</v>
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.2">
@@ -4593,18 +4593,18 @@
         <v>2057</v>
       </c>
       <c r="B39">
-        <v>11.527513410602101</v>
+        <v>36.16483719</v>
       </c>
       <c r="C39">
-        <v>3.5605054064014201</v>
+        <v>28.22622964</v>
       </c>
       <c r="D39">
         <f t="shared" si="9"/>
-        <v>7.9670080042006806</v>
+        <v>7.9386075500000004</v>
       </c>
       <c r="F39" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26413862244</v>
+        <v>261974.04915000001</v>
       </c>
       <c r="G39">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="U39" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012389644711</v>
+        <v>43474.999766635789</v>
       </c>
       <c r="V39">
         <f t="shared" si="6"/>
@@ -4656,11 +4656,11 @@
       </c>
       <c r="W39" s="123">
         <f t="shared" si="7"/>
-        <v>245580.6513934641</v>
+        <v>244643.43640484166</v>
       </c>
       <c r="X39" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77269403936</v>
+        <v>204953.57032842585</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.2">
@@ -4668,18 +4668,18 @@
         <v>2058</v>
       </c>
       <c r="B40">
-        <v>11.5275128900963</v>
+        <v>36.16483771</v>
       </c>
       <c r="C40">
-        <v>3.5605048920739701</v>
+        <v>28.22622329</v>
       </c>
       <c r="D40">
         <f t="shared" si="9"/>
-        <v>7.9670079980223303</v>
+        <v>7.9386144200000004</v>
       </c>
       <c r="F40" s="3">
         <f t="shared" si="10"/>
-        <v>262911.2639347369</v>
+        <v>261974.27585999997</v>
       </c>
       <c r="G40">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="U40" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012353964739</v>
+        <v>43475.039440885776</v>
       </c>
       <c r="V40">
         <f t="shared" si="6"/>
@@ -4731,11 +4731,11 @@
       </c>
       <c r="W40" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65118957855</v>
+        <v>244643.66311484162</v>
       </c>
       <c r="X40" s="123">
         <f t="shared" si="8"/>
-        <v>205726.7725258338</v>
+        <v>204953.75736417584</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.2">
@@ -4743,18 +4743,18 @@
         <v>2059</v>
       </c>
       <c r="B41">
-        <v>11.527512379429</v>
+        <v>36.164838230000001</v>
       </c>
       <c r="C41">
-        <v>3.5605043874681801</v>
+        <v>28.226217120000001</v>
       </c>
       <c r="D41">
         <f t="shared" si="9"/>
-        <v>7.9670079919608199</v>
+        <v>7.9386211099999997</v>
       </c>
       <c r="F41" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26373470708</v>
+        <v>261974.49662999998</v>
       </c>
       <c r="G41">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="U41" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012318959525</v>
+        <v>43475.078075635778</v>
       </c>
       <c r="V41">
         <f t="shared" si="6"/>
@@ -4806,11 +4806,11 @@
       </c>
       <c r="W41" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65098954874</v>
+        <v>244643.88388484163</v>
       </c>
       <c r="X41" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77236080921</v>
+        <v>204953.93949942585</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.2">
@@ -4818,18 +4818,18 @@
         <v>2060</v>
       </c>
       <c r="B42">
-        <v>11.527511878414201</v>
+        <v>36.16483873</v>
       </c>
       <c r="C42">
-        <v>3.5605038924002699</v>
+        <v>28.226211129999999</v>
       </c>
       <c r="D42">
         <f t="shared" si="9"/>
-        <v>7.9670079860139307</v>
+        <v>7.9386276000000002</v>
       </c>
       <c r="F42" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26353845972</v>
+        <v>261974.7108</v>
       </c>
       <c r="G42">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="U42" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012284616234</v>
+        <v>43475.115555385782</v>
       </c>
       <c r="V42">
         <f t="shared" si="6"/>
@@ -4881,11 +4881,11 @@
       </c>
       <c r="W42" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65079330138</v>
+        <v>244644.09805484166</v>
       </c>
       <c r="X42" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77219890512</v>
+        <v>204954.11618967587</v>
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.2">
@@ -4893,18 +4893,18 @@
         <v>2061</v>
       </c>
       <c r="B43">
-        <v>11.5275113868693</v>
+        <v>36.164839219999998</v>
       </c>
       <c r="C43">
-        <v>3.5605034066899899</v>
+        <v>28.226205289999999</v>
       </c>
       <c r="D43">
         <f t="shared" si="9"/>
-        <v>7.9670079801793099</v>
+        <v>7.9386339299999982</v>
       </c>
       <c r="F43" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26334591722</v>
+        <v>261974.91968999992</v>
       </c>
       <c r="G43">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="U43" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012250921296</v>
+        <v>43475.152111135772</v>
       </c>
       <c r="V43">
         <f t="shared" si="6"/>
@@ -4956,11 +4956,11 @@
       </c>
       <c r="W43" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65060075888</v>
+        <v>244644.30694484158</v>
       </c>
       <c r="X43" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77204005758</v>
+        <v>204954.28852392579</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.2">
@@ -4968,18 +4968,18 @@
         <v>2062</v>
       </c>
       <c r="B44">
-        <v>11.5275109046155</v>
+        <v>36.164839710000003</v>
       </c>
       <c r="C44">
-        <v>3.5605029301604301</v>
+        <v>28.22619959</v>
       </c>
       <c r="D44">
         <f t="shared" si="9"/>
-        <v>7.9670079744550701</v>
+        <v>7.9386401200000023</v>
       </c>
       <c r="F44" s="3">
         <f t="shared" si="10"/>
-        <v>262911.2631570173</v>
+        <v>261975.12396000008</v>
       </c>
       <c r="G44">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="U44" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012217863812</v>
+        <v>43475.187858385798</v>
       </c>
       <c r="V44">
         <f t="shared" si="6"/>
@@ -5031,11 +5031,11 @@
       </c>
       <c r="W44" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65041185895</v>
+        <v>244644.51121484174</v>
       </c>
       <c r="X44" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77188421512</v>
+        <v>204954.45704667593</v>
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.2">
@@ -5043,18 +5043,18 @@
         <v>2063</v>
       </c>
       <c r="B45">
-        <v>11.527510431477101</v>
+        <v>36.164840179999999</v>
       </c>
       <c r="C45">
-        <v>3.5605024626380901</v>
+        <v>28.226194020000001</v>
       </c>
       <c r="D45">
         <f t="shared" si="9"/>
-        <v>7.9670079688390105</v>
+        <v>7.9386461599999976</v>
       </c>
       <c r="F45" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26297168736</v>
+        <v>261975.3232799999</v>
       </c>
       <c r="G45">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="U45" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012185431071</v>
+        <v>43475.222739385768</v>
       </c>
       <c r="V45">
         <f t="shared" si="6"/>
@@ -5106,11 +5106,11 @@
       </c>
       <c r="W45" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65022652902</v>
+        <v>244644.71053484155</v>
       </c>
       <c r="X45" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77173131792</v>
+        <v>204954.62148567577</v>
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.2">
@@ -5118,18 +5118,18 @@
         <v>2064</v>
       </c>
       <c r="B46">
-        <v>11.5275099672818</v>
+        <v>36.164840650000002</v>
       </c>
       <c r="C46">
-        <v>3.5605020039526898</v>
+        <v>28.226188570000001</v>
       </c>
       <c r="D46">
         <f t="shared" si="9"/>
-        <v>7.9670079633291095</v>
+        <v>7.9386520800000007</v>
       </c>
       <c r="F46" s="3">
         <f t="shared" si="10"/>
-        <v>262911.2627898606</v>
+        <v>261975.51864000005</v>
       </c>
       <c r="G46">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="U46" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012153611387</v>
+        <v>43475.256927385795</v>
       </c>
       <c r="V46">
         <f t="shared" si="6"/>
@@ -5181,11 +5181,11 @@
       </c>
       <c r="W46" s="123">
         <f t="shared" si="7"/>
-        <v>245580.65004470226</v>
+        <v>244644.90589484171</v>
       </c>
       <c r="X46" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77158131084</v>
+        <v>204954.78265767591</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.2">
@@ -5193,18 +5193,18 @@
         <v>2065</v>
       </c>
       <c r="B47">
-        <v>11.5275095118606</v>
+        <v>36.164841099999997</v>
       </c>
       <c r="C47">
-        <v>3.56050155393722</v>
+        <v>28.22618323</v>
       </c>
       <c r="D47">
         <f t="shared" si="9"/>
-        <v>7.9670079579233803</v>
+        <v>7.9386578699999966</v>
       </c>
       <c r="F47" s="3">
         <f t="shared" si="10"/>
-        <v>262911.26261147152</v>
+        <v>261975.70970999988</v>
       </c>
       <c r="G47">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="U47" s="123">
         <f t="shared" si="5"/>
-        <v>43639.012122393302</v>
+        <v>43475.290364635766</v>
       </c>
       <c r="V47">
         <f t="shared" si="6"/>
@@ -5256,11 +5256,11 @@
       </c>
       <c r="W47" s="123">
         <f t="shared" si="7"/>
-        <v>245580.64986631318</v>
+        <v>244645.09696484153</v>
       </c>
       <c r="X47" s="123">
         <f t="shared" si="8"/>
-        <v>205726.77143413987</v>
+        <v>204954.94029042576</v>
       </c>
     </row>
   </sheetData>
